--- a/VerveStacks_DEU_grids_kan/vt_vervestacks_DEU_v1.xlsx
+++ b/VerveStacks_DEU_grids_kan/vt_vervestacks_DEU_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DF6A9920-CF8E-4FF6-8170-A0F7D24A87F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C12E9F62-AB37-42B7-86F6-A1ED259A76FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{BAAE8584-06B1-4335-A70E-692276180AE3}"/>
+    <workbookView xWindow="3308" yWindow="3308" windowWidth="21600" windowHeight="12682" xr2:uid="{1438A5C3-058A-4651-A9DD-15B08B24AA6B}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -2366,31 +2366,31 @@
     <t>e_w30039908-380</t>
   </si>
   <si>
+    <t>e_w32042992-380</t>
+  </si>
+  <si>
+    <t>e_w95434457-380</t>
+  </si>
+  <si>
     <t>e_w398680313-380</t>
   </si>
   <si>
     <t>e_w59707532-380</t>
   </si>
   <si>
-    <t>e_w95434457-380</t>
-  </si>
-  <si>
-    <t>e_w32042992-380</t>
+    <t>e_DE101-380</t>
+  </si>
+  <si>
+    <t>e_w796306640-380</t>
+  </si>
+  <si>
+    <t>e_w42097854-380</t>
   </si>
   <si>
     <t>e_w953757608-380</t>
   </si>
   <si>
-    <t>e_DE101-380</t>
-  </si>
-  <si>
-    <t>e_w42097854-380</t>
-  </si>
-  <si>
     <t>e_DE42-380</t>
-  </si>
-  <si>
-    <t>e_w796306640-380</t>
   </si>
   <si>
     <t>e_w946969736-380</t>
@@ -5659,7 +5659,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F02E229D-4A47-47E7-BDA4-D1AB1780447E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF1ADA45-7C55-4A1F-894D-10D664AD7FCC}">
   <dimension ref="B9:T348"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -17080,7 +17080,7 @@
         <v>1448</v>
       </c>
       <c r="P213" t="s">
-        <v>1583</v>
+        <v>1712</v>
       </c>
       <c r="Q213" t="s">
         <v>795</v>
@@ -17136,7 +17136,7 @@
         <v>1448</v>
       </c>
       <c r="P214" t="s">
-        <v>1712</v>
+        <v>1583</v>
       </c>
       <c r="Q214" t="s">
         <v>795</v>
@@ -24628,7 +24628,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A10450A6-0456-4E4D-BF6E-7981C01AA92D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCED89B8-ED32-4523-8BAD-38E67011C782}">
   <dimension ref="B9:T161"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -32084,7 +32084,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C53C3DC-880D-4A80-8D34-04118FA261CD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7570041-4C24-462A-937B-624F5AB0A588}">
   <dimension ref="B9:T1322"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -44941,7 +44941,7 @@
         <v>365</v>
       </c>
       <c r="P256" t="s">
-        <v>799</v>
+        <v>960</v>
       </c>
       <c r="Q256" t="s">
         <v>795</v>
@@ -44994,7 +44994,7 @@
         <v>365</v>
       </c>
       <c r="P257" t="s">
-        <v>960</v>
+        <v>799</v>
       </c>
       <c r="Q257" t="s">
         <v>795</v>
@@ -56145,7 +56145,7 @@
         <v>658</v>
       </c>
       <c r="P473" t="s">
-        <v>960</v>
+        <v>799</v>
       </c>
       <c r="Q473" t="s">
         <v>795</v>
@@ -56198,7 +56198,7 @@
         <v>658</v>
       </c>
       <c r="P474" t="s">
-        <v>799</v>
+        <v>960</v>
       </c>
       <c r="Q474" t="s">
         <v>795</v>
@@ -58041,7 +58041,7 @@
         <v>33</v>
       </c>
       <c r="L509">
-        <v>0.14147154991776351</v>
+        <v>0.14147154991776353</v>
       </c>
       <c r="N509" t="s">
         <v>793</v>
@@ -58088,7 +58088,7 @@
         <v>33</v>
       </c>
       <c r="L510">
-        <v>0.14147154991776351</v>
+        <v>0.14147154991776353</v>
       </c>
       <c r="N510" t="s">
         <v>793</v>
@@ -58135,7 +58135,7 @@
         <v>33</v>
       </c>
       <c r="L511">
-        <v>0.14147154991776351</v>
+        <v>0.14147154991776353</v>
       </c>
       <c r="N511" t="s">
         <v>793</v>
@@ -59152,7 +59152,7 @@
         <v>736</v>
       </c>
       <c r="P529" t="s">
-        <v>799</v>
+        <v>960</v>
       </c>
       <c r="Q529" t="s">
         <v>795</v>
@@ -59208,7 +59208,7 @@
         <v>736</v>
       </c>
       <c r="P530" t="s">
-        <v>960</v>
+        <v>799</v>
       </c>
       <c r="Q530" t="s">
         <v>795</v>
@@ -59488,7 +59488,7 @@
         <v>741</v>
       </c>
       <c r="P535" t="s">
-        <v>799</v>
+        <v>960</v>
       </c>
       <c r="Q535" t="s">
         <v>795</v>
@@ -59544,7 +59544,7 @@
         <v>741</v>
       </c>
       <c r="P536" t="s">
-        <v>960</v>
+        <v>799</v>
       </c>
       <c r="Q536" t="s">
         <v>795</v>
@@ -59936,7 +59936,7 @@
         <v>750</v>
       </c>
       <c r="P543" t="s">
-        <v>960</v>
+        <v>799</v>
       </c>
       <c r="Q543" t="s">
         <v>795</v>
@@ -59992,7 +59992,7 @@
         <v>750</v>
       </c>
       <c r="P544" t="s">
-        <v>799</v>
+        <v>960</v>
       </c>
       <c r="Q544" t="s">
         <v>795</v>
@@ -72975,7 +72975,7 @@
         <v>35</v>
       </c>
       <c r="L908">
-        <v>0.14147154991776351</v>
+        <v>0.14147154991776353</v>
       </c>
     </row>
     <row r="909" spans="2:12" x14ac:dyDescent="0.45">
@@ -73010,7 +73010,7 @@
         <v>32</v>
       </c>
       <c r="L909">
-        <v>0.14147154991776351</v>
+        <v>0.14147154991776353</v>
       </c>
     </row>
     <row r="910" spans="2:12" x14ac:dyDescent="0.45">
@@ -73045,7 +73045,7 @@
         <v>32</v>
       </c>
       <c r="L910">
-        <v>0.14147154991776351</v>
+        <v>0.14147154991776353</v>
       </c>
     </row>
     <row r="911" spans="2:12" x14ac:dyDescent="0.45">
@@ -74479,7 +74479,7 @@
         <v>33</v>
       </c>
       <c r="L952">
-        <v>0.30813752321639176</v>
+        <v>0.30813752321639171</v>
       </c>
     </row>
     <row r="953" spans="2:12" x14ac:dyDescent="0.45">
@@ -74505,7 +74505,7 @@
         <v>33</v>
       </c>
       <c r="L953">
-        <v>0.30813752321639176</v>
+        <v>0.30813752321639171</v>
       </c>
     </row>
     <row r="954" spans="2:12" x14ac:dyDescent="0.45">
@@ -74531,7 +74531,7 @@
         <v>33</v>
       </c>
       <c r="L954">
-        <v>0.30813752321639176</v>
+        <v>0.30813752321639171</v>
       </c>
     </row>
     <row r="955" spans="2:12" x14ac:dyDescent="0.45">
@@ -86606,7 +86606,7 @@
         <v>57</v>
       </c>
       <c r="L1299">
-        <v>0.30813752321639176</v>
+        <v>0.30813752321639171</v>
       </c>
     </row>
     <row r="1300" spans="2:12" x14ac:dyDescent="0.45">
@@ -86641,7 +86641,7 @@
         <v>56</v>
       </c>
       <c r="L1300">
-        <v>0.30813752321639176</v>
+        <v>0.30813752321639171</v>
       </c>
     </row>
     <row r="1301" spans="2:12" x14ac:dyDescent="0.45">
@@ -86676,7 +86676,7 @@
         <v>55</v>
       </c>
       <c r="L1301">
-        <v>0.30813752321639176</v>
+        <v>0.30813752321639171</v>
       </c>
     </row>
     <row r="1302" spans="2:12" x14ac:dyDescent="0.45">
@@ -86711,7 +86711,7 @@
         <v>55</v>
       </c>
       <c r="L1302">
-        <v>0.30813752321639176</v>
+        <v>0.30813752321639171</v>
       </c>
     </row>
     <row r="1303" spans="2:12" x14ac:dyDescent="0.45">
@@ -86728,7 +86728,7 @@
         <v>2001</v>
       </c>
       <c r="F1303">
-        <v>1.2E-2</v>
+        <v>2.3E-2</v>
       </c>
       <c r="G1303">
         <v>1</v>
@@ -86737,7 +86737,7 @@
         <v>2376</v>
       </c>
       <c r="I1303">
-        <v>57.20000000000001</v>
+        <v>57.2</v>
       </c>
       <c r="J1303">
         <v>0</v>
@@ -86746,7 +86746,7 @@
         <v>54</v>
       </c>
       <c r="L1303">
-        <v>0.30813752321639176</v>
+        <v>0.30813752321639171</v>
       </c>
     </row>
     <row r="1304" spans="2:12" x14ac:dyDescent="0.45">
@@ -86763,7 +86763,7 @@
         <v>2001</v>
       </c>
       <c r="F1304">
-        <v>2.5999999999999999E-2</v>
+        <v>1.2E-2</v>
       </c>
       <c r="G1304">
         <v>1</v>
@@ -86772,7 +86772,7 @@
         <v>2376</v>
       </c>
       <c r="I1304">
-        <v>57.2</v>
+        <v>57.20000000000001</v>
       </c>
       <c r="J1304">
         <v>0</v>
@@ -86781,7 +86781,7 @@
         <v>54</v>
       </c>
       <c r="L1304">
-        <v>0.30813752321639176</v>
+        <v>0.30813752321639171</v>
       </c>
     </row>
     <row r="1305" spans="2:12" x14ac:dyDescent="0.45">
@@ -86816,7 +86816,7 @@
         <v>54</v>
       </c>
       <c r="L1305">
-        <v>0.30813752321639176</v>
+        <v>0.30813752321639171</v>
       </c>
     </row>
     <row r="1306" spans="2:12" x14ac:dyDescent="0.45">
@@ -86833,7 +86833,7 @@
         <v>2001</v>
       </c>
       <c r="F1306">
-        <v>2.3E-2</v>
+        <v>2.5999999999999999E-2</v>
       </c>
       <c r="G1306">
         <v>1</v>
@@ -86851,7 +86851,7 @@
         <v>54</v>
       </c>
       <c r="L1306">
-        <v>0.30813752321639176</v>
+        <v>0.30813752321639171</v>
       </c>
     </row>
     <row r="1307" spans="2:12" x14ac:dyDescent="0.45">
@@ -86868,7 +86868,7 @@
         <v>2002</v>
       </c>
       <c r="F1307">
-        <v>1.4E-2</v>
+        <v>1.7999999999999999E-2</v>
       </c>
       <c r="G1307">
         <v>1</v>
@@ -86877,7 +86877,7 @@
         <v>2376</v>
       </c>
       <c r="I1307">
-        <v>57.2</v>
+        <v>57.20000000000001</v>
       </c>
       <c r="J1307">
         <v>0</v>
@@ -86886,7 +86886,7 @@
         <v>53</v>
       </c>
       <c r="L1307">
-        <v>0.30813752321639176</v>
+        <v>0.30813752321639171</v>
       </c>
     </row>
     <row r="1308" spans="2:12" x14ac:dyDescent="0.45">
@@ -86903,7 +86903,7 @@
         <v>2002</v>
       </c>
       <c r="F1308">
-        <v>1.7999999999999999E-2</v>
+        <v>1.2999999999999999E-2</v>
       </c>
       <c r="G1308">
         <v>1</v>
@@ -86912,7 +86912,7 @@
         <v>2376</v>
       </c>
       <c r="I1308">
-        <v>57.20000000000001</v>
+        <v>57.2</v>
       </c>
       <c r="J1308">
         <v>0</v>
@@ -86921,7 +86921,7 @@
         <v>53</v>
       </c>
       <c r="L1308">
-        <v>0.30813752321639176</v>
+        <v>0.30813752321639171</v>
       </c>
     </row>
     <row r="1309" spans="2:12" x14ac:dyDescent="0.45">
@@ -86932,13 +86932,13 @@
         <v>730</v>
       </c>
       <c r="D1309" t="s">
-        <v>329</v>
+        <v>155</v>
       </c>
       <c r="E1309">
         <v>2002</v>
       </c>
       <c r="F1309">
-        <v>1.2999999999999999E-2</v>
+        <v>0.02</v>
       </c>
       <c r="G1309">
         <v>1</v>
@@ -86956,7 +86956,7 @@
         <v>53</v>
       </c>
       <c r="L1309">
-        <v>0.30813752321639176</v>
+        <v>0.30813752321639171</v>
       </c>
     </row>
     <row r="1310" spans="2:12" x14ac:dyDescent="0.45">
@@ -86991,7 +86991,7 @@
         <v>53</v>
       </c>
       <c r="L1310">
-        <v>0.30813752321639176</v>
+        <v>0.30813752321639171</v>
       </c>
     </row>
     <row r="1311" spans="2:12" x14ac:dyDescent="0.45">
@@ -87002,7 +87002,7 @@
         <v>730</v>
       </c>
       <c r="D1311" t="s">
-        <v>775</v>
+        <v>782</v>
       </c>
       <c r="E1311">
         <v>2002</v>
@@ -87026,7 +87026,7 @@
         <v>53</v>
       </c>
       <c r="L1311">
-        <v>0.30813752321639176</v>
+        <v>0.30813752321639171</v>
       </c>
     </row>
     <row r="1312" spans="2:12" x14ac:dyDescent="0.45">
@@ -87037,13 +87037,13 @@
         <v>730</v>
       </c>
       <c r="D1312" t="s">
-        <v>632</v>
+        <v>777</v>
       </c>
       <c r="E1312">
         <v>2002</v>
       </c>
       <c r="F1312">
-        <v>0.01</v>
+        <v>1.4E-2</v>
       </c>
       <c r="G1312">
         <v>1</v>
@@ -87061,7 +87061,7 @@
         <v>53</v>
       </c>
       <c r="L1312">
-        <v>0.30813752321639176</v>
+        <v>0.30813752321639171</v>
       </c>
     </row>
     <row r="1313" spans="2:12" x14ac:dyDescent="0.45">
@@ -87072,13 +87072,13 @@
         <v>730</v>
       </c>
       <c r="D1313" t="s">
-        <v>155</v>
+        <v>783</v>
       </c>
       <c r="E1313">
         <v>2002</v>
       </c>
       <c r="F1313">
-        <v>0.02</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="G1313">
         <v>1</v>
@@ -87096,7 +87096,7 @@
         <v>53</v>
       </c>
       <c r="L1313">
-        <v>0.30813752321639176</v>
+        <v>0.30813752321639171</v>
       </c>
     </row>
     <row r="1314" spans="2:12" x14ac:dyDescent="0.45">
@@ -87107,13 +87107,13 @@
         <v>730</v>
       </c>
       <c r="D1314" t="s">
-        <v>782</v>
+        <v>329</v>
       </c>
       <c r="E1314">
         <v>2002</v>
       </c>
       <c r="F1314">
-        <v>2.5000000000000001E-2</v>
+        <v>1.2999999999999999E-2</v>
       </c>
       <c r="G1314">
         <v>1</v>
@@ -87131,7 +87131,7 @@
         <v>53</v>
       </c>
       <c r="L1314">
-        <v>0.30813752321639176</v>
+        <v>0.30813752321639171</v>
       </c>
     </row>
     <row r="1315" spans="2:12" x14ac:dyDescent="0.45">
@@ -87142,13 +87142,13 @@
         <v>730</v>
       </c>
       <c r="D1315" t="s">
-        <v>783</v>
+        <v>632</v>
       </c>
       <c r="E1315">
         <v>2002</v>
       </c>
       <c r="F1315">
-        <v>1.2999999999999999E-2</v>
+        <v>0.01</v>
       </c>
       <c r="G1315">
         <v>1</v>
@@ -87166,7 +87166,7 @@
         <v>53</v>
       </c>
       <c r="L1315">
-        <v>0.30813752321639176</v>
+        <v>0.30813752321639171</v>
       </c>
     </row>
     <row r="1316" spans="2:12" x14ac:dyDescent="0.45">
@@ -87201,7 +87201,7 @@
         <v>52</v>
       </c>
       <c r="L1316">
-        <v>0.30813752321639176</v>
+        <v>0.30813752321639171</v>
       </c>
     </row>
     <row r="1317" spans="2:12" x14ac:dyDescent="0.45">
@@ -87212,13 +87212,13 @@
         <v>730</v>
       </c>
       <c r="D1317" t="s">
-        <v>785</v>
+        <v>21</v>
       </c>
       <c r="E1317">
         <v>2004</v>
       </c>
       <c r="F1317">
-        <v>1.7999999999999999E-2</v>
+        <v>0.01</v>
       </c>
       <c r="G1317">
         <v>1</v>
@@ -87227,7 +87227,7 @@
         <v>2376</v>
       </c>
       <c r="I1317">
-        <v>57.20000000000001</v>
+        <v>57.2</v>
       </c>
       <c r="J1317">
         <v>0</v>
@@ -87236,7 +87236,7 @@
         <v>51</v>
       </c>
       <c r="L1317">
-        <v>0.30813752321639176</v>
+        <v>0.30813752321639171</v>
       </c>
     </row>
     <row r="1318" spans="2:12" x14ac:dyDescent="0.45">
@@ -87247,13 +87247,13 @@
         <v>730</v>
       </c>
       <c r="D1318" t="s">
-        <v>21</v>
+        <v>785</v>
       </c>
       <c r="E1318">
         <v>2004</v>
       </c>
       <c r="F1318">
-        <v>0.01</v>
+        <v>1.7999999999999999E-2</v>
       </c>
       <c r="G1318">
         <v>1</v>
@@ -87262,7 +87262,7 @@
         <v>2376</v>
       </c>
       <c r="I1318">
-        <v>57.2</v>
+        <v>57.20000000000001</v>
       </c>
       <c r="J1318">
         <v>0</v>
@@ -87271,7 +87271,7 @@
         <v>51</v>
       </c>
       <c r="L1318">
-        <v>0.30813752321639176</v>
+        <v>0.30813752321639171</v>
       </c>
     </row>
     <row r="1319" spans="2:12" x14ac:dyDescent="0.45">
@@ -87306,7 +87306,7 @@
         <v>50</v>
       </c>
       <c r="L1319">
-        <v>0.30813752321639176</v>
+        <v>0.30813752321639171</v>
       </c>
     </row>
     <row r="1320" spans="2:12" x14ac:dyDescent="0.45">
@@ -87341,7 +87341,7 @@
         <v>47</v>
       </c>
       <c r="L1320">
-        <v>0.30813752321639176</v>
+        <v>0.30813752321639171</v>
       </c>
     </row>
     <row r="1321" spans="2:12" x14ac:dyDescent="0.45">
@@ -87376,7 +87376,7 @@
         <v>46</v>
       </c>
       <c r="L1321">
-        <v>0.30813752321639176</v>
+        <v>0.30813752321639171</v>
       </c>
     </row>
     <row r="1322" spans="2:12" x14ac:dyDescent="0.45">
@@ -87411,7 +87411,7 @@
         <v>45</v>
       </c>
       <c r="L1322">
-        <v>0.30813752321639176</v>
+        <v>0.30813752321639171</v>
       </c>
     </row>
   </sheetData>
@@ -87420,7 +87420,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05A91634-3F65-4A43-BB96-A91503B864CB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC08EB35-17BF-4AE5-8A94-69AFA8BA59D1}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_DEU_grids_kan/vt_vervestacks_DEU_v1.xlsx
+++ b/VerveStacks_DEU_grids_kan/vt_vervestacks_DEU_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C12E9F62-AB37-42B7-86F6-A1ED259A76FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{509A0FA0-8F63-4140-A150-E84A4FD64E6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3308" yWindow="3308" windowWidth="21600" windowHeight="12682" xr2:uid="{1438A5C3-058A-4651-A9DD-15B08B24AA6B}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{2FECA53D-2624-41D5-A780-8CC5E67D5502}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -2366,31 +2366,31 @@
     <t>e_w30039908-380</t>
   </si>
   <si>
+    <t>e_w95434457-380</t>
+  </si>
+  <si>
+    <t>e_w398680313-380</t>
+  </si>
+  <si>
+    <t>e_w59707532-380</t>
+  </si>
+  <si>
     <t>e_w32042992-380</t>
   </si>
   <si>
-    <t>e_w95434457-380</t>
-  </si>
-  <si>
-    <t>e_w398680313-380</t>
-  </si>
-  <si>
-    <t>e_w59707532-380</t>
+    <t>e_w796306640-380</t>
   </si>
   <si>
     <t>e_DE101-380</t>
   </si>
   <si>
-    <t>e_w796306640-380</t>
+    <t>e_w953757608-380</t>
+  </si>
+  <si>
+    <t>e_DE42-380</t>
   </si>
   <si>
     <t>e_w42097854-380</t>
-  </si>
-  <si>
-    <t>e_w953757608-380</t>
-  </si>
-  <si>
-    <t>e_DE42-380</t>
   </si>
   <si>
     <t>e_w946969736-380</t>
@@ -5659,7 +5659,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF1ADA45-7C55-4A1F-894D-10D664AD7FCC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60C97C64-5782-450F-846E-BC9B129AFE93}">
   <dimension ref="B9:T348"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -24628,7 +24628,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCED89B8-ED32-4523-8BAD-38E67011C782}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{391E949D-BD23-42FA-AE06-E636D197DC44}">
   <dimension ref="B9:T161"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -32084,7 +32084,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7570041-4C24-462A-937B-624F5AB0A588}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2DCCFB8-B785-47FC-921C-771DC4F241ED}">
   <dimension ref="B9:T1322"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -44941,7 +44941,7 @@
         <v>365</v>
       </c>
       <c r="P256" t="s">
-        <v>960</v>
+        <v>799</v>
       </c>
       <c r="Q256" t="s">
         <v>795</v>
@@ -44994,7 +44994,7 @@
         <v>365</v>
       </c>
       <c r="P257" t="s">
-        <v>799</v>
+        <v>960</v>
       </c>
       <c r="Q257" t="s">
         <v>795</v>
@@ -55969,7 +55969,7 @@
         <v>652</v>
       </c>
       <c r="P469" t="s">
-        <v>960</v>
+        <v>799</v>
       </c>
       <c r="Q469" t="s">
         <v>795</v>
@@ -56013,7 +56013,7 @@
         <v>652</v>
       </c>
       <c r="P470" t="s">
-        <v>799</v>
+        <v>960</v>
       </c>
       <c r="Q470" t="s">
         <v>795</v>
@@ -56145,7 +56145,7 @@
         <v>658</v>
       </c>
       <c r="P473" t="s">
-        <v>799</v>
+        <v>960</v>
       </c>
       <c r="Q473" t="s">
         <v>795</v>
@@ -56198,7 +56198,7 @@
         <v>658</v>
       </c>
       <c r="P474" t="s">
-        <v>960</v>
+        <v>799</v>
       </c>
       <c r="Q474" t="s">
         <v>795</v>
@@ -58041,7 +58041,7 @@
         <v>33</v>
       </c>
       <c r="L509">
-        <v>0.14147154991776353</v>
+        <v>0.14147154991776351</v>
       </c>
       <c r="N509" t="s">
         <v>793</v>
@@ -58088,7 +58088,7 @@
         <v>33</v>
       </c>
       <c r="L510">
-        <v>0.14147154991776353</v>
+        <v>0.14147154991776351</v>
       </c>
       <c r="N510" t="s">
         <v>793</v>
@@ -58135,7 +58135,7 @@
         <v>33</v>
       </c>
       <c r="L511">
-        <v>0.14147154991776353</v>
+        <v>0.14147154991776351</v>
       </c>
       <c r="N511" t="s">
         <v>793</v>
@@ -59264,7 +59264,7 @@
         <v>737</v>
       </c>
       <c r="P531" t="s">
-        <v>799</v>
+        <v>960</v>
       </c>
       <c r="Q531" t="s">
         <v>795</v>
@@ -59320,7 +59320,7 @@
         <v>737</v>
       </c>
       <c r="P532" t="s">
-        <v>960</v>
+        <v>799</v>
       </c>
       <c r="Q532" t="s">
         <v>795</v>
@@ -59824,7 +59824,7 @@
         <v>748</v>
       </c>
       <c r="P541" t="s">
-        <v>799</v>
+        <v>960</v>
       </c>
       <c r="Q541" t="s">
         <v>795</v>
@@ -59880,7 +59880,7 @@
         <v>748</v>
       </c>
       <c r="P542" t="s">
-        <v>960</v>
+        <v>799</v>
       </c>
       <c r="Q542" t="s">
         <v>795</v>
@@ -59936,7 +59936,7 @@
         <v>750</v>
       </c>
       <c r="P543" t="s">
-        <v>799</v>
+        <v>960</v>
       </c>
       <c r="Q543" t="s">
         <v>795</v>
@@ -59992,7 +59992,7 @@
         <v>750</v>
       </c>
       <c r="P544" t="s">
-        <v>960</v>
+        <v>799</v>
       </c>
       <c r="Q544" t="s">
         <v>795</v>
@@ -72975,7 +72975,7 @@
         <v>35</v>
       </c>
       <c r="L908">
-        <v>0.14147154991776353</v>
+        <v>0.14147154991776351</v>
       </c>
     </row>
     <row r="909" spans="2:12" x14ac:dyDescent="0.45">
@@ -72986,13 +72986,13 @@
         <v>610</v>
       </c>
       <c r="D909" t="s">
-        <v>429</v>
+        <v>683</v>
       </c>
       <c r="E909">
         <v>2023</v>
       </c>
       <c r="F909">
-        <v>1.4199999999999999E-2</v>
+        <v>1.35E-2</v>
       </c>
       <c r="G909">
         <v>1</v>
@@ -73010,7 +73010,7 @@
         <v>32</v>
       </c>
       <c r="L909">
-        <v>0.14147154991776353</v>
+        <v>0.14147154991776351</v>
       </c>
     </row>
     <row r="910" spans="2:12" x14ac:dyDescent="0.45">
@@ -73021,13 +73021,13 @@
         <v>610</v>
       </c>
       <c r="D910" t="s">
-        <v>683</v>
+        <v>429</v>
       </c>
       <c r="E910">
         <v>2023</v>
       </c>
       <c r="F910">
-        <v>1.35E-2</v>
+        <v>1.4199999999999999E-2</v>
       </c>
       <c r="G910">
         <v>1</v>
@@ -73045,7 +73045,7 @@
         <v>32</v>
       </c>
       <c r="L910">
-        <v>0.14147154991776353</v>
+        <v>0.14147154991776351</v>
       </c>
     </row>
     <row r="911" spans="2:12" x14ac:dyDescent="0.45">
@@ -73176,7 +73176,7 @@
         <v>33</v>
       </c>
       <c r="L914">
-        <v>0.5466383247903186</v>
+        <v>0.54663832479031849</v>
       </c>
     </row>
     <row r="915" spans="2:12" x14ac:dyDescent="0.45">
@@ -73202,7 +73202,7 @@
         <v>33</v>
       </c>
       <c r="L915">
-        <v>0.5466383247903186</v>
+        <v>0.54663832479031849</v>
       </c>
     </row>
     <row r="916" spans="2:12" x14ac:dyDescent="0.45">
@@ -73228,7 +73228,7 @@
         <v>33</v>
       </c>
       <c r="L916">
-        <v>0.5466383247903186</v>
+        <v>0.54663832479031849</v>
       </c>
     </row>
     <row r="917" spans="2:12" x14ac:dyDescent="0.45">
@@ -74479,7 +74479,7 @@
         <v>33</v>
       </c>
       <c r="L952">
-        <v>0.30813752321639171</v>
+        <v>0.30813752321639176</v>
       </c>
     </row>
     <row r="953" spans="2:12" x14ac:dyDescent="0.45">
@@ -74505,7 +74505,7 @@
         <v>33</v>
       </c>
       <c r="L953">
-        <v>0.30813752321639171</v>
+        <v>0.30813752321639176</v>
       </c>
     </row>
     <row r="954" spans="2:12" x14ac:dyDescent="0.45">
@@ -74531,7 +74531,7 @@
         <v>33</v>
       </c>
       <c r="L954">
-        <v>0.30813752321639171</v>
+        <v>0.30813752321639176</v>
       </c>
     </row>
     <row r="955" spans="2:12" x14ac:dyDescent="0.45">
@@ -86606,7 +86606,7 @@
         <v>57</v>
       </c>
       <c r="L1299">
-        <v>0.30813752321639171</v>
+        <v>0.30813752321639176</v>
       </c>
     </row>
     <row r="1300" spans="2:12" x14ac:dyDescent="0.45">
@@ -86641,7 +86641,7 @@
         <v>56</v>
       </c>
       <c r="L1300">
-        <v>0.30813752321639171</v>
+        <v>0.30813752321639176</v>
       </c>
     </row>
     <row r="1301" spans="2:12" x14ac:dyDescent="0.45">
@@ -86652,13 +86652,13 @@
         <v>730</v>
       </c>
       <c r="D1301" t="s">
-        <v>774</v>
+        <v>155</v>
       </c>
       <c r="E1301">
         <v>2000</v>
       </c>
       <c r="F1301">
-        <v>1.2E-2</v>
+        <v>1.2999999999999999E-2</v>
       </c>
       <c r="G1301">
         <v>1</v>
@@ -86667,7 +86667,7 @@
         <v>2376</v>
       </c>
       <c r="I1301">
-        <v>57.20000000000001</v>
+        <v>57.2</v>
       </c>
       <c r="J1301">
         <v>0</v>
@@ -86676,7 +86676,7 @@
         <v>55</v>
       </c>
       <c r="L1301">
-        <v>0.30813752321639171</v>
+        <v>0.30813752321639176</v>
       </c>
     </row>
     <row r="1302" spans="2:12" x14ac:dyDescent="0.45">
@@ -86687,13 +86687,13 @@
         <v>730</v>
       </c>
       <c r="D1302" t="s">
-        <v>155</v>
+        <v>774</v>
       </c>
       <c r="E1302">
         <v>2000</v>
       </c>
       <c r="F1302">
-        <v>1.2999999999999999E-2</v>
+        <v>1.2E-2</v>
       </c>
       <c r="G1302">
         <v>1</v>
@@ -86702,7 +86702,7 @@
         <v>2376</v>
       </c>
       <c r="I1302">
-        <v>57.2</v>
+        <v>57.20000000000001</v>
       </c>
       <c r="J1302">
         <v>0</v>
@@ -86711,7 +86711,7 @@
         <v>55</v>
       </c>
       <c r="L1302">
-        <v>0.30813752321639171</v>
+        <v>0.30813752321639176</v>
       </c>
     </row>
     <row r="1303" spans="2:12" x14ac:dyDescent="0.45">
@@ -86728,7 +86728,7 @@
         <v>2001</v>
       </c>
       <c r="F1303">
-        <v>2.3E-2</v>
+        <v>1.2E-2</v>
       </c>
       <c r="G1303">
         <v>1</v>
@@ -86737,7 +86737,7 @@
         <v>2376</v>
       </c>
       <c r="I1303">
-        <v>57.2</v>
+        <v>57.20000000000001</v>
       </c>
       <c r="J1303">
         <v>0</v>
@@ -86746,7 +86746,7 @@
         <v>54</v>
       </c>
       <c r="L1303">
-        <v>0.30813752321639171</v>
+        <v>0.30813752321639176</v>
       </c>
     </row>
     <row r="1304" spans="2:12" x14ac:dyDescent="0.45">
@@ -86781,7 +86781,7 @@
         <v>54</v>
       </c>
       <c r="L1304">
-        <v>0.30813752321639171</v>
+        <v>0.30813752321639176</v>
       </c>
     </row>
     <row r="1305" spans="2:12" x14ac:dyDescent="0.45">
@@ -86798,7 +86798,7 @@
         <v>2001</v>
       </c>
       <c r="F1305">
-        <v>1.2E-2</v>
+        <v>2.5999999999999999E-2</v>
       </c>
       <c r="G1305">
         <v>1</v>
@@ -86807,7 +86807,7 @@
         <v>2376</v>
       </c>
       <c r="I1305">
-        <v>57.20000000000001</v>
+        <v>57.2</v>
       </c>
       <c r="J1305">
         <v>0</v>
@@ -86816,7 +86816,7 @@
         <v>54</v>
       </c>
       <c r="L1305">
-        <v>0.30813752321639171</v>
+        <v>0.30813752321639176</v>
       </c>
     </row>
     <row r="1306" spans="2:12" x14ac:dyDescent="0.45">
@@ -86833,7 +86833,7 @@
         <v>2001</v>
       </c>
       <c r="F1306">
-        <v>2.5999999999999999E-2</v>
+        <v>2.3E-2</v>
       </c>
       <c r="G1306">
         <v>1</v>
@@ -86851,7 +86851,7 @@
         <v>54</v>
       </c>
       <c r="L1306">
-        <v>0.30813752321639171</v>
+        <v>0.30813752321639176</v>
       </c>
     </row>
     <row r="1307" spans="2:12" x14ac:dyDescent="0.45">
@@ -86868,7 +86868,7 @@
         <v>2002</v>
       </c>
       <c r="F1307">
-        <v>1.7999999999999999E-2</v>
+        <v>1.2999999999999999E-2</v>
       </c>
       <c r="G1307">
         <v>1</v>
@@ -86877,7 +86877,7 @@
         <v>2376</v>
       </c>
       <c r="I1307">
-        <v>57.20000000000001</v>
+        <v>57.2</v>
       </c>
       <c r="J1307">
         <v>0</v>
@@ -86886,7 +86886,7 @@
         <v>53</v>
       </c>
       <c r="L1307">
-        <v>0.30813752321639171</v>
+        <v>0.30813752321639176</v>
       </c>
     </row>
     <row r="1308" spans="2:12" x14ac:dyDescent="0.45">
@@ -86903,7 +86903,7 @@
         <v>2002</v>
       </c>
       <c r="F1308">
-        <v>1.2999999999999999E-2</v>
+        <v>1.7999999999999999E-2</v>
       </c>
       <c r="G1308">
         <v>1</v>
@@ -86912,7 +86912,7 @@
         <v>2376</v>
       </c>
       <c r="I1308">
-        <v>57.2</v>
+        <v>57.20000000000001</v>
       </c>
       <c r="J1308">
         <v>0</v>
@@ -86921,7 +86921,7 @@
         <v>53</v>
       </c>
       <c r="L1308">
-        <v>0.30813752321639171</v>
+        <v>0.30813752321639176</v>
       </c>
     </row>
     <row r="1309" spans="2:12" x14ac:dyDescent="0.45">
@@ -86932,13 +86932,13 @@
         <v>730</v>
       </c>
       <c r="D1309" t="s">
-        <v>155</v>
+        <v>781</v>
       </c>
       <c r="E1309">
         <v>2002</v>
       </c>
       <c r="F1309">
-        <v>0.02</v>
+        <v>1.4E-2</v>
       </c>
       <c r="G1309">
         <v>1</v>
@@ -86956,7 +86956,7 @@
         <v>53</v>
       </c>
       <c r="L1309">
-        <v>0.30813752321639171</v>
+        <v>0.30813752321639176</v>
       </c>
     </row>
     <row r="1310" spans="2:12" x14ac:dyDescent="0.45">
@@ -86967,13 +86967,13 @@
         <v>730</v>
       </c>
       <c r="D1310" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="E1310">
         <v>2002</v>
       </c>
       <c r="F1310">
-        <v>1.4E-2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="G1310">
         <v>1</v>
@@ -86991,7 +86991,7 @@
         <v>53</v>
       </c>
       <c r="L1310">
-        <v>0.30813752321639171</v>
+        <v>0.30813752321639176</v>
       </c>
     </row>
     <row r="1311" spans="2:12" x14ac:dyDescent="0.45">
@@ -87002,13 +87002,13 @@
         <v>730</v>
       </c>
       <c r="D1311" t="s">
-        <v>782</v>
+        <v>155</v>
       </c>
       <c r="E1311">
         <v>2002</v>
       </c>
       <c r="F1311">
-        <v>1.4E-2</v>
+        <v>0.02</v>
       </c>
       <c r="G1311">
         <v>1</v>
@@ -87026,7 +87026,7 @@
         <v>53</v>
       </c>
       <c r="L1311">
-        <v>0.30813752321639171</v>
+        <v>0.30813752321639176</v>
       </c>
     </row>
     <row r="1312" spans="2:12" x14ac:dyDescent="0.45">
@@ -87037,13 +87037,13 @@
         <v>730</v>
       </c>
       <c r="D1312" t="s">
-        <v>777</v>
+        <v>329</v>
       </c>
       <c r="E1312">
         <v>2002</v>
       </c>
       <c r="F1312">
-        <v>1.4E-2</v>
+        <v>1.2999999999999999E-2</v>
       </c>
       <c r="G1312">
         <v>1</v>
@@ -87061,7 +87061,7 @@
         <v>53</v>
       </c>
       <c r="L1312">
-        <v>0.30813752321639171</v>
+        <v>0.30813752321639176</v>
       </c>
     </row>
     <row r="1313" spans="2:12" x14ac:dyDescent="0.45">
@@ -87072,13 +87072,13 @@
         <v>730</v>
       </c>
       <c r="D1313" t="s">
-        <v>783</v>
+        <v>632</v>
       </c>
       <c r="E1313">
         <v>2002</v>
       </c>
       <c r="F1313">
-        <v>2.5000000000000001E-2</v>
+        <v>0.01</v>
       </c>
       <c r="G1313">
         <v>1</v>
@@ -87096,7 +87096,7 @@
         <v>53</v>
       </c>
       <c r="L1313">
-        <v>0.30813752321639171</v>
+        <v>0.30813752321639176</v>
       </c>
     </row>
     <row r="1314" spans="2:12" x14ac:dyDescent="0.45">
@@ -87107,13 +87107,13 @@
         <v>730</v>
       </c>
       <c r="D1314" t="s">
-        <v>329</v>
+        <v>783</v>
       </c>
       <c r="E1314">
         <v>2002</v>
       </c>
       <c r="F1314">
-        <v>1.2999999999999999E-2</v>
+        <v>1.4E-2</v>
       </c>
       <c r="G1314">
         <v>1</v>
@@ -87131,7 +87131,7 @@
         <v>53</v>
       </c>
       <c r="L1314">
-        <v>0.30813752321639171</v>
+        <v>0.30813752321639176</v>
       </c>
     </row>
     <row r="1315" spans="2:12" x14ac:dyDescent="0.45">
@@ -87142,13 +87142,13 @@
         <v>730</v>
       </c>
       <c r="D1315" t="s">
-        <v>632</v>
+        <v>776</v>
       </c>
       <c r="E1315">
         <v>2002</v>
       </c>
       <c r="F1315">
-        <v>0.01</v>
+        <v>1.4E-2</v>
       </c>
       <c r="G1315">
         <v>1</v>
@@ -87166,7 +87166,7 @@
         <v>53</v>
       </c>
       <c r="L1315">
-        <v>0.30813752321639171</v>
+        <v>0.30813752321639176</v>
       </c>
     </row>
     <row r="1316" spans="2:12" x14ac:dyDescent="0.45">
@@ -87201,7 +87201,7 @@
         <v>52</v>
       </c>
       <c r="L1316">
-        <v>0.30813752321639171</v>
+        <v>0.30813752321639176</v>
       </c>
     </row>
     <row r="1317" spans="2:12" x14ac:dyDescent="0.45">
@@ -87236,7 +87236,7 @@
         <v>51</v>
       </c>
       <c r="L1317">
-        <v>0.30813752321639171</v>
+        <v>0.30813752321639176</v>
       </c>
     </row>
     <row r="1318" spans="2:12" x14ac:dyDescent="0.45">
@@ -87271,7 +87271,7 @@
         <v>51</v>
       </c>
       <c r="L1318">
-        <v>0.30813752321639171</v>
+        <v>0.30813752321639176</v>
       </c>
     </row>
     <row r="1319" spans="2:12" x14ac:dyDescent="0.45">
@@ -87306,7 +87306,7 @@
         <v>50</v>
       </c>
       <c r="L1319">
-        <v>0.30813752321639171</v>
+        <v>0.30813752321639176</v>
       </c>
     </row>
     <row r="1320" spans="2:12" x14ac:dyDescent="0.45">
@@ -87341,7 +87341,7 @@
         <v>47</v>
       </c>
       <c r="L1320">
-        <v>0.30813752321639171</v>
+        <v>0.30813752321639176</v>
       </c>
     </row>
     <row r="1321" spans="2:12" x14ac:dyDescent="0.45">
@@ -87376,7 +87376,7 @@
         <v>46</v>
       </c>
       <c r="L1321">
-        <v>0.30813752321639171</v>
+        <v>0.30813752321639176</v>
       </c>
     </row>
     <row r="1322" spans="2:12" x14ac:dyDescent="0.45">
@@ -87411,7 +87411,7 @@
         <v>45</v>
       </c>
       <c r="L1322">
-        <v>0.30813752321639171</v>
+        <v>0.30813752321639176</v>
       </c>
     </row>
   </sheetData>
@@ -87420,7 +87420,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC08EB35-17BF-4AE5-8A94-69AFA8BA59D1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDF83F8F-CD8A-4E7F-88B0-1751BBDC78FD}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>
